--- a/example/128H100-RoCE/excel/ipaddress.xlsx
+++ b/example/128H100-RoCE/excel/ipaddress.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP规划地址表-参数网" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP规划地址表-存储网" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP规划地址表-业务网" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP规划地址表-带外网" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="环回地址表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网段规划表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IP规划地址表-参数网" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IP规划地址表-存储网" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IP规划地址表-业务网" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IP规划地址表-带外网" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="环回地址表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="网段规划表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,22 +55,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -455,57 +446,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>己端设备</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>己端接口</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>己端IP地址</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>己端IP长度</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>己端AS</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>对端设备</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>对端接口</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>对端IP地址</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>对端IP长度</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>对端AS</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注信息</t>
         </is>
@@ -25627,57 +25618,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>己端设备</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>己端接口</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>己端IP地址</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>己端IP长度</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>己端AS</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>对端设备</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>对端接口</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>对端IP地址</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>对端IP长度</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>对端AS</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注信息</t>
         </is>
@@ -25809,57 +25800,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>己端设备</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>己端接口</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>己端IP地址</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>己端IP长度</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>己端AS</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>对端设备</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>对端接口</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>对端IP地址</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>对端IP长度</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>对端AS</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注信息</t>
         </is>
@@ -26285,57 +26276,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>己端设备</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>己端接口</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>己端IP地址</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>己端IP长度</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>己端AS</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>对端设备</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>对端接口</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>对端IP地址</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>对端IP长度</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>对端AS</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注信息</t>
         </is>
@@ -26460,22 +26451,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>己端设备</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>环回接口</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>环回IP</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>环回长度</t>
         </is>
@@ -26981,17 +26972,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>网段用途</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>网段</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>掩码</t>
         </is>
